--- a/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
+++ b/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8b9eab14d89956a8/3d Printing Stuff/Models/SV08 Mods/SV08 AWD Live Idlers Front Tensioners - Final/Printed Version/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_DFF688E9926BEE6F6450CCD7565DCE3A87C03B69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C272D8FA-017C-496C-A6E1-24E1BA0760A1}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="11_DFF688E9926BEE6F6450CCD7565DCE3A87C03B69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36EC1B92-0323-4BDC-93AC-3015D06D29B3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51720" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consolidated BOM" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,6 @@
     <t>SV08-P6 Dual Shear Live Idlers Front Tensioners (Printed 6mm) — BOM (Extracted from STEP)</t>
   </si>
   <si>
-    <t>From the STEP tree. Z Carriages excluded, D2F-L switches counted as one unit each. Printed-plate version: all 12 plates are under Printed Parts. No open items. Hidden imported-model parts (e.g. the Xol carriage shim) are intentionally excluded. Purchase Links not merged (Drive file not pointed to this run).</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
     <t>Linear Rails &amp; Sliders</t>
   </si>
   <si>
-    <t>MG9H Linear Rail Slide</t>
-  </si>
-  <si>
     <t>Y MGN9H Rail 402mm</t>
   </si>
   <si>
@@ -286,9 +280,6 @@
     <t>Gantry Y-Axis 2020 Extrusion 469mm</t>
   </si>
   <si>
-    <t>Gantry X-Axis 2020 Extrusion 357mm</t>
-  </si>
-  <si>
     <t>Shortened from 345mm: all tensioning now happens at the front motor mounts.</t>
   </si>
   <si>
@@ -331,12 +322,6 @@
     <t>Back Right Top Plate Printed6mm</t>
   </si>
   <si>
-    <t>Front Left Bottom Dual Shear Live Idler Tensioner Dual Lever</t>
-  </si>
-  <si>
-    <t>Front Left Top Dual Shear Live Idler Tensioner Dual Lever</t>
-  </si>
-  <si>
     <t>Front Right Bottom Printed6mm</t>
   </si>
   <si>
@@ -488,6 +473,21 @@
   </si>
   <si>
     <t>6mm OD is more common and acceptable. Purchase preferred. Printed as alternative with same dimensions.</t>
+  </si>
+  <si>
+    <t>From the STEP tree. Z Carriages excluded, D2F-L switches counted as one unit each. Printed-plate version: all 12 plates are under Printed Parts. No open items. Hidden imported-model parts (e.g. the Xol carriage shim) are intentionally excluded.</t>
+  </si>
+  <si>
+    <t>Gantry X-Axis 2020 Extrusion 342mm</t>
+  </si>
+  <si>
+    <t>Front Left Bottom Printed6mm</t>
+  </si>
+  <si>
+    <t>Front Left Top Printed6mm</t>
+  </si>
+  <si>
+    <t>MGN9H Linear Rail Slide</t>
   </si>
 </sst>
 </file>
@@ -589,9 +589,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -610,6 +610,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -908,7 +912,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
@@ -918,7 +922,7 @@
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>1</v>
+        <v>151</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -927,24 +931,24 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -953,161 +957,161 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="3">
         <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="3">
         <v>4</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" s="3">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1116,58 +1120,58 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="3">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>4</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="3">
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1176,37 +1180,37 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="3">
         <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="3">
         <v>28</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="D22" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1215,24 +1219,24 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="3">
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D24" t="s">
-        <v>124</v>
-      </c>
-      <c r="E24" s="4" t="s">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1241,24 +1245,24 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="3">
         <v>2</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="4" t="s">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1267,37 +1271,37 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="3">
         <v>4</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="3">
         <v>4</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>122</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D29" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1306,24 +1310,24 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3">
         <v>36</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" s="4" t="s">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1332,71 +1336,71 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="3">
         <v>44</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="D33" t="s">
-        <v>129</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B34" s="3">
         <v>38</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="3">
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="3">
         <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="D36" t="s">
-        <v>131</v>
-      </c>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1405,39 +1409,39 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="3">
         <v>48</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D38" t="s">
-        <v>132</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B39" s="3">
         <v>4</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="D39" t="s">
-        <v>133</v>
-      </c>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1446,39 +1450,39 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" s="3">
         <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42" s="3">
         <v>2</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="D42" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1487,37 +1491,37 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B44" s="3">
         <v>1</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" s="3">
         <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" t="s">
+        <v>130</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="D45" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="2"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1526,92 +1530,92 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47" s="3">
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48" s="3">
         <v>8</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" s="3">
         <v>2</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50" s="3">
         <v>2</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51" s="3">
         <v>1</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="D51" t="s">
-        <v>151</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -1620,109 +1624,109 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53" s="3">
         <v>4</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B54" s="3">
         <v>2</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B55" s="3">
         <v>2</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B56" s="3">
         <v>2</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B57" s="3">
         <v>1</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B58" s="3">
         <v>1</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -1731,24 +1735,24 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B60" s="3">
         <v>2</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D60" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E60" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -1757,67 +1761,67 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B62" s="3">
         <v>2</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B63" s="3">
         <v>2</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B64" s="3">
         <v>1</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B65" s="3">
         <v>1</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>84</v>
+      <c r="A66" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -1826,20 +1830,20 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B67" s="3">
         <v>4</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>86</v>
+      <c r="A68" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -1848,48 +1852,48 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B69" s="3">
         <v>2</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B70" s="3">
         <v>1</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B71" s="3">
         <v>1</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>91</v>
+      <c r="A72" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -1898,291 +1902,298 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B73" s="3">
         <v>4</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B74" s="3">
         <v>4</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B75" s="3">
         <v>4</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B76" s="3">
         <v>2</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B77" s="3">
         <v>2</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B78" s="3">
         <v>2</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B79" s="3">
         <v>2</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B80" s="3">
         <v>1</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B81" s="3">
         <v>1</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B82" s="3">
         <v>1</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B83" s="3">
         <v>1</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B84" s="3">
         <v>1</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B85" s="3">
         <v>1</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B86" s="3">
         <v>1</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B87" s="3">
         <v>1</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B88" s="3">
         <v>1</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B89" s="3">
         <v>1</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B90" s="3">
         <v>1</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B91" s="3">
         <v>1</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A25:E25"/>
@@ -2195,14 +2206,7 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A66:E66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
+++ b/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Ultra-thin head (.8-1mm). 2 per front motor assembly and 2 per XY joint.</t>
+          <t>Ultra-thin head (.8-1mm). 2 per front motor assembly and 2 per XY joint. Use threadlocker: blue (medium, removable) recommended; red (high strength) only for a permanent build, since removing it takes heat that can damage bearings and printed parts.</t>
         </is>
       </c>
     </row>

--- a/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
+++ b/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="6" min="1" max="1"/>
@@ -506,7 +506,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -943,7 +942,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint.</t>
+          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build.</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1120,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>M3 Washer (3mm ID | 7mm OD | .5mm Tall)</t>
+          <t>M3 Washer (3mm ID | 7mm OD | .5-.6mm Tall)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1840,17 +1839,17 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Spacer 5mm Printed6mm</t>
+          <t>XY Live Idler Spacer 10mm Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Check Repo</t>
+          <t>One per XY joint, between the bottom plate and the X extrusion (replaces the two stacked 5 mm spacers).</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1969,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Back Left Bottom Plate Printed6mm</t>
+          <t>Back Left Bottom Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D80" s="2" t="n"/>
@@ -1991,7 +1990,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Back Left Top Plate Printed6mm</t>
+          <t>Back Left Top Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D81" s="2" t="n"/>
@@ -2012,7 +2011,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Back Right Bottom Plate Printed6mm</t>
+          <t>Back Right Bottom Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D82" s="2" t="n"/>
@@ -2033,7 +2032,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Back Right Top Plate Printed6mm</t>
+          <t>Back Right Top Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D83" s="2" t="n"/>
@@ -2054,7 +2053,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Front Left Bottom Printed6mm</t>
+          <t>Front Left Bottom Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D84" s="2" t="n"/>
@@ -2075,7 +2074,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Front Left Top Printed6mm</t>
+          <t>Front Left Top Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D85" s="2" t="n"/>
@@ -2096,7 +2095,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Front Right Bottom Printed6mm</t>
+          <t>Front Right Bottom Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D86" s="2" t="n"/>
@@ -2117,7 +2116,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Front Right Top Printed6mm</t>
+          <t>Front Right Top Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D87" s="2" t="n"/>
@@ -2138,7 +2137,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Left Bottom Plate Printed6mm</t>
+          <t>XY Live Idler Left Bottom Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D88" s="2" t="n"/>
@@ -2159,7 +2158,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Left Top Plate Printed6mm</t>
+          <t>XY Live Idler Left Top Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D89" s="2" t="n"/>
@@ -2180,7 +2179,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Right Bottom Plate Printed6mm</t>
+          <t>XY Live Idler Right Bottom Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D90" s="2" t="n"/>
@@ -2201,7 +2200,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Right Top Plate Printed6mm</t>
+          <t>XY Live Idler Right Top Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D91" s="2" t="n"/>
@@ -2211,6 +2210,9 @@
         </is>
       </c>
     </row>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A30:E30"/>

--- a/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
+++ b/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="6" min="1" max="1"/>
@@ -506,6 +506,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -942,7 +943,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build.</t>
+          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build. UNDER REVIEW: the linked spacers measure about 5.05 mm across (anodised aluminium), too big for the 4.992-5.000 mm bore of a 695 bearing, so they won't slide in. We're evaluating replacements. If you already have them, sand the last ~2 mm of each end (the only part that goes into the bearings) down to about 4.990-4.995 mm: spin it in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go, and stop when it presses into a bearing with firm thumb pressure. Don't force an oversize spacer in; that loads the bearing balls.</t>
         </is>
       </c>
     </row>
@@ -967,7 +968,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Replaces the M5 x 30mm dowel in the front motor assemblies (1 per side). Held by 2x M3 x 10mm Ultra Thin Flat Head.</t>
+          <t>Replaces the M5 x 30mm dowel in the front motor assemblies (1 per side). Held by 2x M3 x 10mm Ultra Thin Flat Head. UNDER REVIEW: the linked spacers measure about 5.05 mm across (anodised aluminium), too big for the 4.992-5.000 mm bore of a 695 bearing, so they won't slide in. We're evaluating replacements. If you already have them, sand the last ~2 mm of each end (the only part that goes into the bearings) down to about 4.990-4.995 mm: spin it in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go, and stop when it presses into a bearing with firm thumb pressure. Don't force an oversize spacer in; that loads the bearing balls.</t>
         </is>
       </c>
     </row>
@@ -2210,9 +2211,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A30:E30"/>

--- a/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
+++ b/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build. UNDER REVIEW: the linked spacers measure about 5.05 mm across (anodised aluminium), too big for the 4.992-5.000 mm bore of a 695 bearing, so they won't slide in. We're evaluating replacements. If you already have them, sand the last ~2 mm of each end (the only part that goes into the bearings) down to about 4.990-4.995 mm: spin it in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go, and stop when it presses into a bearing with firm thumb pressure. Don't force an oversize spacer in; that loads the bearing balls.</t>
+          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build. UNDER REVIEW: the linked spacers measure about 5.05 mm across (anodised aluminium), too big for the 4.992-5.000 mm bore of a 695 bearing, so they won't slide in. We're evaluating replacements. If you already have them, sand the last ~2 mm of each end (the only part that goes into the bearings) down to about 4.990-4.995 mm: spin it in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go, and stop when it presses into a bearing with firm thumb pressure. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 40 mm long, works in place of the spacer and its two flat-head screws. At 40 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Replaces the M5 x 30mm dowel in the front motor assemblies (1 per side). Held by 2x M3 x 10mm Ultra Thin Flat Head. UNDER REVIEW: the linked spacers measure about 5.05 mm across (anodised aluminium), too big for the 4.992-5.000 mm bore of a 695 bearing, so they won't slide in. We're evaluating replacements. If you already have them, sand the last ~2 mm of each end (the only part that goes into the bearings) down to about 4.990-4.995 mm: spin it in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go, and stop when it presses into a bearing with firm thumb pressure. Don't force an oversize spacer in; that loads the bearing balls.</t>
+          <t>Replaces the M5 x 30mm dowel in the front motor assemblies (1 per side). Held by 2x M3 x 10mm Ultra Thin Flat Head. UNDER REVIEW: the linked spacers measure about 5.05 mm across (anodised aluminium), too big for the 4.992-5.000 mm bore of a 695 bearing, so they won't slide in. We're evaluating replacements. If you already have them, sand the last ~2 mm of each end (the only part that goes into the bearings) down to about 4.990-4.995 mm: spin it in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go, and stop when it presses into a bearing with firm thumb pressure. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 30 mm long, works in place of the spacer and its two flat-head screws. At 30 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
         </is>
       </c>
     </row>

--- a/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
+++ b/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build. UNDER REVIEW: the linked spacers measure about 5.05 mm across (anodised aluminium), too big for the 4.992-5.000 mm bore of a 695 bearing, so they won't slide in. We're evaluating replacements. If you already have them, sand the last ~2 mm of each end (the only part that goes into the bearings) down to about 4.990-4.995 mm: spin it in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go, and stop when it presses into a bearing with firm thumb pressure. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 40 mm long, works in place of the spacer and its two flat-head screws. At 40 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
+          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build. FIT NOTE: the spacers measure about 5.05 mm across (anodised aluminium), a little too big for the 4.992-5.000 mm bore of a 695 bearing, so sand the whole length of each spacer down to fit, not just the ends: the toothed pulley or idler has to slide along the shaft to reach its place between the bearings, and sanding only the last 5 mm of each end isn't enough. This is common practice in the 3D printing community, and it's confirmed working on the v2 test build. Spin the spacer in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go (aim for about 4.990-4.995 mm), and stop when it presses into a bearing with firm thumb pressure and the pulley slides over it. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 40 mm long, works in place of the spacer and its two flat-head screws. At 40 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. Test-fit each dowel in a bearing before assembly and sand or grind it to size the same way if it's tight. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Replaces the M5 x 30mm dowel in the front motor assemblies (1 per side). Held by 2x M3 x 10mm Ultra Thin Flat Head. UNDER REVIEW: the linked spacers measure about 5.05 mm across (anodised aluminium), too big for the 4.992-5.000 mm bore of a 695 bearing, so they won't slide in. We're evaluating replacements. If you already have them, sand the last ~2 mm of each end (the only part that goes into the bearings) down to about 4.990-4.995 mm: spin it in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go, and stop when it presses into a bearing with firm thumb pressure. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 30 mm long, works in place of the spacer and its two flat-head screws. At 30 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
+          <t>Replaces the M5 x 30mm dowel in the front motor assemblies (1 per side). Held by 2x M3 x 10mm Ultra Thin Flat Head. FIT NOTE: the spacers measure about 5.05 mm across (anodised aluminium), a little too big for the 4.992-5.000 mm bore of a 695 bearing, so sand the whole length of each spacer down to fit, not just the ends: the toothed pulley or idler has to slide along the shaft to reach its place between the bearings, and sanding only the last 5 mm of each end isn't enough. This is common practice in the 3D printing community, and it's confirmed working on the v2 test build. Spin the spacer in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go (aim for about 4.990-4.995 mm), and stop when it presses into a bearing with firm thumb pressure and the pulley slides over it. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 30 mm long, works in place of the spacer and its two flat-head screws. At 30 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. Test-fit each dowel in a bearing before assembly and sand or grind it to size the same way if it's tight. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
         </is>
       </c>
     </row>

--- a/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
+++ b/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="6" min="1" max="1"/>
@@ -534,14 +534,14 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" s="6">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Fasteners - Screws</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" s="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
@@ -552,84 +552,80 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>M3 x 8mm SHCS</t>
+          <t>M4 x 10mm BHCS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0F5Q6YYWM</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Count matches the 28 M3 T-Nuts 1:1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>https://amazon.com/dp/B0CTH3Z2F5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7" s="6">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>M4 x 10mm BHCS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0CTH3Z2F5</t>
+          <t>M3 x 6mm FHCS</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B01E5EOIWW</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" s="6">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>M3 x 6mm FHCS</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B01E5EOIWW</t>
+          <t>M3 x 10mm BHCS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0GJK7Z9DH</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" s="6">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>M3 x 10mm BHCS</t>
+          <t>M3 x 35mm SHCS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0GJK7Z9DH</t>
+          <t>https://amazon.com/dp/B0GHY9ZCLC</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" s="6">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
@@ -640,17 +636,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>M3 x 35mm SHCS</t>
+          <t>M4 x 45mm BHCS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0GHY9ZCLC</t>
+          <t>https://amazon.com/dp/B0GH6G1R1G</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" s="6">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
@@ -661,42 +657,46 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>M4 x 45mm BHCS</t>
+          <t>M3 x 10mm Ultra Thin Flat Head (.8-1mm)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0GH6G1R1G</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n"/>
-    </row>
-    <row r="12">
+          <t>https://amazon.com/dp/B0H61WCTBX</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Ultra-thin head (.8-1mm). 2 per front motor assembly and 2 per XY joint. Use threadlocker: blue (medium, removable) recommended; red (high strength) only for a permanent build, since removing it takes heat that can damage bearings and printed parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" s="6">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>M3 x 10mm Ultra Thin Flat Head (.8-1mm)</t>
+          <t>M2 x 2mm Set Screw</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0H61WCTBX</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Ultra-thin head (.8-1mm). 2 per front motor assembly and 2 per XY joint. Use threadlocker: blue (medium, removable) recommended; red (high strength) only for a permanent build, since removing it takes heat that can damage bearings and printed parts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>https://amazon.com/dp/B0DDJBSF6B</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Should come with the GT2 20-Tooth Pulley - Live Idler Version (2 per pulley, 4 total).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" s="6">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
@@ -707,21 +707,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>M2 x 2mm Set Screw</t>
+          <t>M2 x 8mm SHCS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0DDJBSF6B</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Should come with the GT2 20-Tooth Pulley - Live Idler Version (2 per pulley, 4 total).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>https://amazon.com/dp/B0D4JMPT86</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14" s="6">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
@@ -732,17 +728,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>M2 x 8mm SHCS</t>
+          <t>M4 x 20mm BHCS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0D4JMPT86</t>
+          <t>https://amazon.com/dp/B0DYSQZHC9</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" s="6">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Screws</t>
@@ -753,56 +749,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>M4 x 20mm BHCS</t>
+          <t>M5 x 45mm BHCS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0DYSQZHC9</t>
+          <t>https://amazon.com/dp/B0GJX8PR8J</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Screws</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
+    <row r="16" s="6">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Fasteners - Shoulder Bolts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" s="6">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Shoulder Bolts</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>D5 M3 x 30mm Shoulder Bolt</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.us/item/3256810189139611.html</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Make sure you select Size D5-M3, Length 30mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" s="6">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Shoulder Bolts</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>M5 x 45mm BHCS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0GJX8PR8J</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Fasteners - Shoulder Bolts</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Shoulder Bolts</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>D5 M3 x 30mm Shoulder Bolt</t>
+          <t>D5 M3 x 25mm Shoulder Bolt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -812,11 +812,11 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Make sure you select Size D5-M3, Length 30mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>Make sure you select Size D5-M3, Length 25mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" s="6">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Shoulder Bolts</t>
@@ -827,7 +827,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>D5 M3 x 25mm Shoulder Bolt</t>
+          <t>D5 M3 x 35mm Shoulder Bolt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -837,627 +837,631 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Make sure you select Size D5-M3, Length 25mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Shoulder Bolts</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
+          <t>Make sure you select Size D5-M3, Length 35mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" s="6">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Fasteners - T-Nuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" s="6">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>T-Nuts</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>M4 T-Nut</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0C9DJBG1H</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n"/>
+    </row>
+    <row r="22" s="6">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Fasteners - Threaded Rods</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" s="6">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Threaded Rods</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>M3 Internally Threaded Spacer (5mm OD | 35mm Tall)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0D3HWQ2GF</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build. FIT NOTE: the spacers measure about 5.05 mm across (anodised aluminium), a little too big for the 4.992-5.000 mm bore of a 695 bearing, so sand the whole length of each spacer down to fit, not just the ends: the toothed pulley or idler has to slide along the shaft to reach its place between the bearings, and sanding only the last 5 mm of each end isn't enough. This is common practice in the 3D printing community, and it's confirmed working on the v2 test build. Spin the spacer in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go (aim for about 4.990-4.995 mm), and stop when it presses into a bearing with firm thumb pressure and the pulley slides over it. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 40 mm long, works in place of the spacer and its two flat-head screws. At 40 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. Test-fit each dowel in a bearing before assembly and sand or grind it to size the same way if it's tight. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" s="6">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Threaded Rods</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>M3 Internally Threaded Spacer (5mm OD | 25mm Tall)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0D3HVVJPN</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Replaces the M5 x 30mm dowel in the front motor assemblies (1 per side). Held by 2x M3 x 10mm Ultra Thin Flat Head. FIT NOTE: the spacers measure about 5.05 mm across (anodised aluminium), a little too big for the 4.992-5.000 mm bore of a 695 bearing, so sand the whole length of each spacer down to fit, not just the ends: the toothed pulley or idler has to slide along the shaft to reach its place between the bearings, and sanding only the last 5 mm of each end isn't enough. This is common practice in the 3D printing community, and it's confirmed working on the v2 test build. Spin the spacer in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go (aim for about 4.990-4.995 mm), and stop when it presses into a bearing with firm thumb pressure and the pulley slides over it. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 30 mm long, works in place of the spacer and its two flat-head screws. At 30 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. Test-fit each dowel in a bearing before assembly and sand or grind it to size the same way if it's tight. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" s="6">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Fasteners - Nuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" s="6">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Nuts</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>D5 M3 x 35mm Shoulder Bolt</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256810189139611.html</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Make sure you select Size D5-M3, Length 35mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Fasteners - T-Nuts</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>T-Nuts</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>M4 T-Nut</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0C9DJBG1H</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>T-Nuts</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>M3 T-Nut</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0G2M7W3PL</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Fasteners - Threaded Rods</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Threaded Rods</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>M2 Nut</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0FGTMN5JM</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n"/>
+    </row>
+    <row r="27" s="6">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Nuts</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>M5 Nut</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0D1X2YBLJ</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n"/>
+    </row>
+    <row r="28" s="6">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Inserts - Heat-Set</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" s="6">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Heat-Set</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>M3 Heat Set Insert (Voron Spec)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0DG59PW2R</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>36 total: 6 in each XY Joint, 8 in each Front assembly, 4 in each Back assembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" s="6">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Washers &amp; Shims</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="6">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Washers &amp; Shims</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>M5 Washer (5mm ID | 10mm OD | 1mm Tall)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B07WZ5WQCG</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Includes the 36 bearing-stack shims, now named M5 Washer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" s="6">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Washers &amp; Shims</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>M4 Washer (4mm ID | 9mm OD | 1mm Tall)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0DK6KXB6W</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>.8mm more common and acceptable swap, OD matters</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" s="6">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Washers &amp; Shims</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>M3 Washer (3mm ID | 7mm OD | .5-.6mm Tall)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0C3TJ7PWT</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n"/>
+    </row>
+    <row r="34" s="6">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Washers &amp; Shims</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>M3 Shim (3mm ID | 5mm OD | .2mm Tall)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B08ZYP1TK4</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
+    </row>
+    <row r="35" s="6">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Bearings</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" s="6">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Bearings</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>695-2RS Flanged Bearing</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0CGXF48ZZ</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Includes the 12 loose bearings named F695-2RS Bearing Single in CAD (36 stacked + 12 loose).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" s="6">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Bearings</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>MR63ZZ Bearing 3x6x2.5mm</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0DY11G865</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n"/>
+    </row>
+    <row r="38" s="6">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Pulleys</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" s="6">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Pulleys</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>GT2 20-Tooth Pulley Set-Screw Version</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0GWLM6FD6</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n"/>
+    </row>
+    <row r="40" s="6">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Pulleys</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>M3 Internally Threaded Spacer (5mm OD | 35mm Tall)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0D3HWQ2GF</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build. FIT NOTE: the spacers measure about 5.05 mm across (anodised aluminium), a little too big for the 4.992-5.000 mm bore of a 695 bearing, so sand the whole length of each spacer down to fit, not just the ends: the toothed pulley or idler has to slide along the shaft to reach its place between the bearings, and sanding only the last 5 mm of each end isn't enough. This is common practice in the 3D printing community, and it's confirmed working on the v2 test build. Spin the spacer in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go (aim for about 4.990-4.995 mm), and stop when it presses into a bearing with firm thumb pressure and the pulley slides over it. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 40 mm long, works in place of the spacer and its two flat-head screws. At 40 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. Test-fit each dowel in a bearing before assembly and sand or grind it to size the same way if it's tight. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Threaded Rods</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>GT2 20-Tooth Pulley - Live Idler Version</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.us/item/3256803833151466.html</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Make sure you select Bore 5mm Width 6mm. Uses 2x M2 x 2mm Set Screws each (4 total). Pulley body recovered from an unnamed STEP node (one per XY Joint)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" s="6">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Belts</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" s="6">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Belts</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Bottom Belt 2.1m</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B07CDDPCM8</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n"/>
+    </row>
+    <row r="43" s="6">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Belts</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Top Belt 2.1m</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B07CDDPCM8</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n"/>
+    </row>
+    <row r="44" s="6">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Spacers (Aluminum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" s="6">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Spacers (Aluminum)</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>M5 Spacer 10mm OD 10mm Tall</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.com/item/3256802878592600.html</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>8mm OD is more common and acceptable. Purchase preferred. Printed as alternative with same dimensions.. If purchasing from Aliexpress be sure to select 5.1x10x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" s="6">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Spacers (Aluminum)</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>M3 Spacer 8mm OD 20mm Tall</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0F8QLBKYC</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>6mm OD is more common and acceptable. Purchase preferred. Printed as alternative with same dimensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" s="6">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Spacers (Aluminum)</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>M3 Internally Threaded Spacer (5mm OD | 25mm Tall)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0D3HVVJPN</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Replaces the M5 x 30mm dowel in the front motor assemblies (1 per side). Held by 2x M3 x 10mm Ultra Thin Flat Head. FIT NOTE: the spacers measure about 5.05 mm across (anodised aluminium), a little too big for the 4.992-5.000 mm bore of a 695 bearing, so sand the whole length of each spacer down to fit, not just the ends: the toothed pulley or idler has to slide along the shaft to reach its place between the bearings, and sanding only the last 5 mm of each end isn't enough. This is common practice in the 3D printing community, and it's confirmed working on the v2 test build. Spin the spacer in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go (aim for about 4.990-4.995 mm), and stop when it presses into a bearing with firm thumb pressure and the pulley slides over it. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 30 mm long, works in place of the spacer and its two flat-head screws. At 30 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. Test-fit each dowel in a bearing before assembly and sand or grind it to size the same way if it's tight. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Fasteners - Nuts</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Nuts</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>M5 Spacer 8mm OD 20mm Tall</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0CRL77N5C</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Purchase preferred. Printed as alternative with same dimensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" s="6">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Spacers (Aluminum)</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>M5 Spacer 8mm OD 30mm Tall</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0CQ53LS2B</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Purchase preferred. Printed as alternative with same dimensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" s="6">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Spacers (Aluminum)</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>M5 Spacer 10mm OD 20mm Tall</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0D2L3H5LV</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>8mm OD is more common and acceptable. Purchase preferred. Printed as alternative with same dimensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" s="6">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Xol Toolhead Hardware</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" s="6">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Xol Toolhead Hardware</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>M2 Nut</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0FGTMN5JM</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Nuts</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>M5 Nut</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0D1X2YBLJ</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Inserts - Heat-Set</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Heat-Set</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>M3 Heat Set Insert (Voron Spec)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0DG59PW2R</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>36 total: 6 in each XY Joint, 8 in each Front assembly, 4 in each Back assembly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Washers &amp; Shims</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Washers &amp; Shims</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>M5 Washer (5mm ID | 10mm OD | 1mm Tall)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B07WZ5WQCG</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Includes the 36 bearing-stack shims, now named M5 Washer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Washers &amp; Shims</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>M4 Washer (4mm ID | 9mm OD | 1mm Tall)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0DK6KXB6W</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>.8mm more common and acceptable swap, OD matters</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Washers &amp; Shims</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>M3 Washer (3mm ID | 7mm OD | .5-.6mm Tall)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0C3TJ7PWT</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Washers &amp; Shims</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>M3 Shim (3mm ID | 5mm OD | .2mm Tall)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B08ZYP1TK4</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Bearings</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Bearings</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>695-2RS Flanged Bearing</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0CGXF48ZZ</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Includes the 12 loose bearings named F695-2RS Bearing Single in CAD (36 stacked + 12 loose).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Bearings</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>MR63ZZ Bearing 3x6x2.5mm</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0DY11G865</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Pulleys</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Pulleys</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>GT2 20-Tooth Pulley Set-Screw Version</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0GWLM6FD6</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Pulleys</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>M3 x 6mm BHCS</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Not required unless building the Xol carriage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" s="6">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Xol Toolhead Hardware</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>GT2 20-Tooth Pulley - Live Idler Version</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.us/item/3256803833151466.html</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Make sure you select Bore 5mm Width 6mm. Uses 2x M2 x 2mm Set Screws each (4 total). Pulley body recovered from an unnamed STEP node (one per XY Joint)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Belts</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Belts</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Bottom Belt 2.1m</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B07CDDPCM8</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Belts</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Top Belt 2.1m</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B07CDDPCM8</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Spacers (Aluminum)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Spacers (Aluminum)</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>M5 Spacer 10mm OD 10mm Tall</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.com/item/3256802878592600.html</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>8mm OD is more common and acceptable. Purchase preferred. Printed as alternative with same dimensions.. If purchasing from Aliexpress be sure to select 5.1x10x10</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Spacers (Aluminum)</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>M3 Spacer 8mm OD 20mm Tall</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0F8QLBKYC</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>6mm OD is more common and acceptable. Purchase preferred. Printed as alternative with same dimensions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Spacers (Aluminum)</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>M2 x 12mm BHCS</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Not required unless building the Xol carriage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" s="6">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Xol Toolhead Hardware</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>M5 Spacer 8mm OD 20mm Tall</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0CRL77N5C</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Purchase preferred. Printed as alternative with same dimensions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Spacers (Aluminum)</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>M5 Spacer 8mm OD 30mm Tall</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0CQ53LS2B</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Purchase preferred. Printed as alternative with same dimensions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Spacers (Aluminum)</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>M5 Spacer 10mm OD 20mm Tall</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0D2L3H5LV</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>8mm OD is more common and acceptable. Purchase preferred. Printed as alternative with same dimensions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Xol Toolhead Hardware</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Xol Toolhead Hardware</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>M3 x 6mm BHCS</t>
+          <t>M3 x 30mm Dowel Pin</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1467,11 +1471,11 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Not required unless building the Xol carriage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
+          <t>Only dowel used by the Xol Toolhead. Not required unless building the Xol carriage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" s="6">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Xol Toolhead Hardware</t>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>M2 x 12mm BHCS</t>
+          <t>Xol 6mm Clamp</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1496,117 +1500,99 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" s="6">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Xol Toolhead Hardware</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>D2F-L Micro Switch (Endstop)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Not required unless building the Xol carriage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" s="6">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Xol Toolhead Hardware</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Xol-Carriage_MGN12H_MGN9H_archetype_clips</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Not required unless building the Xol carriage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" s="6">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Electronics / Endstops</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" s="6">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Electronics / Endstops</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>M3 x 30mm Dowel Pin</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Only dowel used by the Xol Toolhead. Not required unless building the Xol carriage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Xol Toolhead Hardware</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Xol 6mm Clamp</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>Not required unless building the Xol carriage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Xol Toolhead Hardware</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>D2F-L Micro Switch (Endstop)</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Not required unless building the Xol carriage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Xol Toolhead Hardware</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Xol-Carriage_MGN12H_MGN9H_archetype_clips</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0DBV8XGG4</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Not required unless building the Xol carriage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+          <t>Base machine endstops (one in each back assembly).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" s="6">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Electronics / Endstops</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
+          <t>Linear Rails &amp; Sliders</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" s="6">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Electronics / Endstops</t>
+          <t>Linear Rails &amp; Sliders</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
@@ -1614,39 +1600,49 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>D2F-L Micro Switch (Endstop)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://amazon.com/dp/B0DBV8XGG4</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Base machine endstops (one in each back assembly).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+          <t>MGN9H Linear Rail Slide</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Re-usable from Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" s="6">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Linear Rails &amp; Sliders</t>
         </is>
       </c>
-    </row>
-    <row r="62">
+      <c r="B61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Y MGN9H Rail 402mm</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Re-usable from Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" s="6">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Linear Rails &amp; Sliders</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>MGN9H Linear Rail Slide</t>
+          <t>MGN12H Linear Rail Slide</t>
         </is>
       </c>
       <c r="D62" s="2" t="n"/>
@@ -1656,18 +1652,18 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" s="6">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Linear Rails &amp; Sliders</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Y MGN9H Rail 402mm</t>
+          <t>X MGN12H Rail 406mm</t>
         </is>
       </c>
       <c r="D63" s="2" t="n"/>
@@ -1677,118 +1673,112 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Linear Rails &amp; Sliders</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>MGN12H Linear Rail Slide</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Re-usable from Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
+    <row r="64" s="6">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Linear Rail Mounting Hardware</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" s="6">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Linear Rails &amp; Sliders</t>
+          <t>Linear Rail Mounting Hardware</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>X MGN12H Rail 406mm</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n"/>
+          <t>M3 x 8mm SHCS</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0F5Q6YYWM</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Re-usable from Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+          <t>Rail mounting screws: 10 per Y rail (20) and 8 on the X rail, one per M3 T-Nut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" s="6">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Linear Rail Mounting Hardware</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>M3 T-Nut</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>https://amazon.com/dp/B0G2M7W3PL</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Rail mounting T-nuts: 10 per Y rail (20) and 8 on the X rail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" s="6">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>Motors</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68" s="6">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Motors</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B68" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>42-48 Motor 5mmx30-37mm Shaft</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+    </row>
+    <row r="69" s="6">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>Extrusions</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70" s="6">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Extrusions</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n">
+      <c r="B70" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Gantry Y-Axis 2020 Extrusion 469mm</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Extrusions</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Gantry X-Axis 2020 Extrusion 342mm</t>
-        </is>
-      </c>
       <c r="D70" s="2" t="n"/>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Shortened from 345mm: all tensioning now happens at the front motor mounts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
+      <c r="E70" s="2" t="n"/>
+    </row>
+    <row r="71" s="6">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Extrusions</t>
@@ -1799,94 +1789,94 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>Gantry X-Axis 2020 Extrusion 342mm</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Shortened from 345mm: all tensioning now happens at the front motor mounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" s="6">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Extrusions</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
           <t>Toolhead X-Axis 2020 Extrusion 426mm</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+    </row>
+    <row r="73" s="6">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>Printed Parts</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74" s="6">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n">
+      <c r="B74" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Tensioner Lever Arm Revised</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Check Repo</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Printed Parts</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>XY Live Idler Spacer 10mm Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>One per XY joint, between the bottom plate and the X extrusion (replaces the two stacked 5 mm spacers).</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
+          <t>Check Repo</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" s="6">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Z Carriage Spacer</t>
+          <t>XY Live Idler Spacer 10mm Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Check Repo</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
+          <t>One per XY joint, between the bottom plate and the X extrusion (replaces the two stacked 5 mm spacers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" s="6">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Back Spacer Plate 20mm</t>
+          <t>Z Carriage Spacer</t>
         </is>
       </c>
       <c r="D76" s="2" t="n"/>
@@ -1896,7 +1886,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" s="6">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -1907,7 +1897,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Front Spacer Plate 20mm</t>
+          <t>Back Spacer Plate 20mm</t>
         </is>
       </c>
       <c r="D77" s="2" t="n"/>
@@ -1917,7 +1907,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" s="6">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -1928,7 +1918,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Printed Back Motor Spacer</t>
+          <t>Front Spacer Plate 20mm</t>
         </is>
       </c>
       <c r="D78" s="2" t="n"/>
@@ -1938,7 +1928,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" s="6">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -1949,7 +1939,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Spacer</t>
+          <t>Printed Back Motor Spacer</t>
         </is>
       </c>
       <c r="D79" s="2" t="n"/>
@@ -1959,18 +1949,18 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" s="6">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Back Left Bottom Plate Printed6mm - For Printing</t>
+          <t>XY Live Idler Spacer</t>
         </is>
       </c>
       <c r="D80" s="2" t="n"/>
@@ -1980,7 +1970,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" s="6">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -1991,7 +1981,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Back Left Top Plate Printed6mm - For Printing</t>
+          <t>Back Left Bottom Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D81" s="2" t="n"/>
@@ -2001,7 +1991,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" s="6">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2012,7 +2002,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Back Right Bottom Plate Printed6mm - For Printing</t>
+          <t>Back Left Top Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D82" s="2" t="n"/>
@@ -2022,7 +2012,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" s="6">
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2033,7 +2023,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Back Right Top Plate Printed6mm - For Printing</t>
+          <t>Back Right Bottom Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D83" s="2" t="n"/>
@@ -2043,7 +2033,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" s="6">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2054,7 +2044,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Front Left Bottom Printed6mm - For Printing</t>
+          <t>Back Right Top Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D84" s="2" t="n"/>
@@ -2064,7 +2054,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" s="6">
       <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2075,7 +2065,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Front Left Top Printed6mm - For Printing</t>
+          <t>Front Left Bottom Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D85" s="2" t="n"/>
@@ -2085,7 +2075,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" s="6">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2096,7 +2086,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Front Right Bottom Printed6mm - For Printing</t>
+          <t>Front Left Top Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D86" s="2" t="n"/>
@@ -2106,7 +2096,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" s="6">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2117,7 +2107,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Front Right Top Printed6mm - For Printing</t>
+          <t>Front Right Bottom Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D87" s="2" t="n"/>
@@ -2127,7 +2117,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" s="6">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2138,7 +2128,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Left Bottom Plate Printed6mm - For Printing</t>
+          <t>Front Right Top Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D88" s="2" t="n"/>
@@ -2148,7 +2138,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" s="6">
       <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2159,7 +2149,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Left Top Plate Printed6mm - For Printing</t>
+          <t>XY Live Idler Left Bottom Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D89" s="2" t="n"/>
@@ -2169,7 +2159,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" s="6">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2180,7 +2170,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Right Bottom Plate Printed6mm - For Printing</t>
+          <t>XY Live Idler Left Top Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D90" s="2" t="n"/>
@@ -2190,7 +2180,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" s="6">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Printed Parts</t>
@@ -2201,7 +2191,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>XY Live Idler Right Top Plate Printed6mm - For Printing</t>
+          <t>XY Live Idler Right Bottom Plate Printed6mm - For Printing</t>
         </is>
       </c>
       <c r="D91" s="2" t="n"/>
@@ -2211,27 +2201,49 @@
         </is>
       </c>
     </row>
+    <row r="92" s="6">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Printed Parts</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>XY Live Idler Right Top Plate Printed6mm - For Printing</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Check Repo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
+++ b/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>6mm OD is more common and acceptable. Purchase preferred. Printed as alternative with same dimensions.</t>
+          <t>6mm OD is more common and acceptable. Purchase preferred. Printed as alternative with same dimensions. Optional: use a 6mm OD (or smaller) spacer for the one nearest each end of the Gantry X extrusion (2 total) and the stock 345mm extrusion fits without cutting.</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,11 @@
         </is>
       </c>
       <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Stock extrusion works: the front and back motor-mount bolt holes line up with its existing holes.</t>
+        </is>
+      </c>
     </row>
     <row r="71" s="6">
       <c r="A71" s="2" t="inlineStr">
@@ -1795,7 +1799,7 @@
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Shortened from 345mm: all tensioning now happens at the front motor mounts.</t>
+          <t>Shortened from 345mm: all tensioning now happens at the front motor mounts. The back motor-mount bolt holes line up with the stock extrusion's existing holes. To use the stock 345mm extrusion without cutting it, fit a 6mm OD (or smaller) M3 x 20mm spacer in the spot nearest each end of this extrusion (one per back corner) instead of an 8mm one.</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1818,11 @@
         </is>
       </c>
       <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Stock extrusion works: the XY joint bolt holes line up with its existing holes (5mm and 25mm from each end).</t>
+        </is>
+      </c>
     </row>
     <row r="73" s="6">
       <c r="A73" s="7" t="inlineStr">

--- a/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
+++ b/Printed Version/SV08_P6_Printed_BOM_from_STEP.xlsx
@@ -653,21 +653,21 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>M3 x 10mm Ultra Thin Flat Head (.8-1mm)</t>
+          <t>M4x8 Ultra Thin Flat Head</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0H61WCTBX</t>
+          <t>https://amazon.com/dp/B0H61X7SWB</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Ultra-thin head (.8-1mm). 2 per front motor assembly and 2 per XY joint. Use threadlocker: blue (medium, removable) recommended; red (high strength) only for a permanent build, since removing it takes heat that can damage bearings and printed parts.</t>
+          <t>Screw end of each Chicago bolt live idler shaft (1 per front motor assembly and 1 per XY joint). 1.2mm head, thin enough to clear the front motors. Use threadlocker: blue (medium, removable) recommended; red (high strength) only for a permanent build, since removing it takes heat that can damage bearings and printed parts.</t>
         </is>
       </c>
     </row>
@@ -872,14 +872,14 @@
     <row r="22" s="6">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Fasteners - Threaded Rods</t>
+          <t>Live Idler Shafts</t>
         </is>
       </c>
     </row>
     <row r="23" s="6">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Threaded Rods</t>
+          <t>Live Idler Shafts</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -887,24 +887,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>M3 Internally Threaded Spacer (5mm OD | 35mm Tall)</t>
+          <t>M5x40 Chicago Bolt Base</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0D3HWQ2GF</t>
+          <t>https://amazon.com/dp/B0FLJNY14R</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Replaces the M5 x 40mm dowel in the XY Joints (1 per joint). Clamped between the plates by 2x M3 x 10mm Ultra Thin Flat Head per joint. It reaches 1.5 mm into each bearing. A 40 mm spacer would run through both bearings for their full width, but the 35 mm is kept so the same part fits every version of the build. FIT NOTE: the spacers measure about 5.05 mm across (anodised aluminium), a little too big for the 4.992-5.000 mm bore of a 695 bearing, so sand the whole length of each spacer down to fit, not just the ends: the toothed pulley or idler has to slide along the shaft to reach its place between the bearings, and sanding only the last 5 mm of each end isn't enough. This is common practice in the 3D printing community, and it's confirmed working on the v2 test build. Spin the spacer in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go (aim for about 4.990-4.995 mm), and stop when it presses into a bearing with firm thumb pressure and the pulley slides over it. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 40 mm long, works in place of the spacer and its two flat-head screws. At 40 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. Test-fit each dowel in a bearing before assembly and sand or grind it to size the same way if it's tight. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
+          <t>Live idler shaft in the XY joints (1 per joint). 304 stainless Chicago screw: the 5mm x 40mm barrel runs the full width of both bearings, its head on one bearing and an M4x8 Ultra Thin Flat Head on the other, so the bearings are clamped and the idler can't float. Pack of 20. The M4x4 screws in the pack aren't used: their 2mm heads don't clear the front motors, so the ultra-thin heads are used everywhere. ALTERNATIVES (not as good): an M3 internally threaded spacer, 5mm OD x 35mm (amazon.com/dp/B0D3HWQ2GF), clamped by 2x M3 x 10mm ultra-thin flat heads (amazon.com/dp/B0H61WCTBX). The anodised spacers measure about 5.05mm, so sand the whole length in a drill (400-600 grit) until it presses into a bearing with firm thumb pressure and the pulley slides over it. Or a 5mm h6/h7 slip-fit dowel / ground shaft, 40mm long: it fits, but it's held only by the pulley set screws, so the idler can float up and down under belt tension, which causes vibration.</t>
         </is>
       </c>
     </row>
     <row r="24" s="6">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Threaded Rods</t>
+          <t>Live Idler Shafts</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -912,17 +912,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>M3 Internally Threaded Spacer (5mm OD | 25mm Tall)</t>
+          <t>M5x30 Chicago Bolt Base</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0D3HVVJPN</t>
+          <t>https://amazon.com/dp/B0FLJQP39V</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Replaces the M5 x 30mm dowel in the front motor assemblies (1 per side). Held by 2x M3 x 10mm Ultra Thin Flat Head. FIT NOTE: the spacers measure about 5.05 mm across (anodised aluminium), a little too big for the 4.992-5.000 mm bore of a 695 bearing, so sand the whole length of each spacer down to fit, not just the ends: the toothed pulley or idler has to slide along the shaft to reach its place between the bearings, and sanding only the last 5 mm of each end isn't enough. This is common practice in the 3D printing community, and it's confirmed working on the v2 test build. Spin the spacer in a drill against 400-600 grit, or roll it under a flat block on sandpaper laid on the bench. Measure in two directions as you go (aim for about 4.990-4.995 mm), and stop when it presses into a bearing with firm thumb pressure and the pulley slides over it. Don't force an oversize spacer in; that loads the bearing balls. ALTERNATIVE: a 5 mm dowel pin, 30 mm long, works in place of the spacer and its two flat-head screws. At 30 mm it runs the full width of both bearings, flush with their outer faces. Get h6/h7 (slip-fit) dowels or a cut length of 5 mm ground linear shaft (h6/g6): standard m6 press-fit dowels are 5.004-5.012 mm and will jam in the bearing just like the oversize spacers. Test-fit each dowel in a bearing before assembly and sand or grind it to size the same way if it's tight. The pulley's set screws hold the dowel in place, and the pulley sits between the two bearings.</t>
+          <t>Live idler shaft in the front motor assemblies (1 per side). 304 stainless Chicago screw: the 5mm x 30mm barrel runs the full width of both bearings, head at the bottom and an M4x8 Ultra Thin Flat Head at the top, 0.4mm under the motor. Pack of 20; the M4x4 screws in the pack aren't used (their 2mm heads don't clear the motor). ALTERNATIVES (not as good): an M3 internally threaded spacer, 5mm OD x 25mm (amazon.com/dp/B0D3HVVJPN), clamped by 2x M3 x 10mm ultra-thin flat heads (amazon.com/dp/B0H61WCTBX). The anodised spacers measure about 5.05mm, so sand the whole length in a drill (400-600 grit) until it presses into a bearing with firm thumb pressure and the pulley slides over it. Or a 5mm h6/h7 slip-fit dowel / ground shaft, 30mm long: it fits, but it's held only by the pulley set screws, so the idler can float up and down under belt tension, which causes vibration.</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Shortened from 345mm: all tensioning now happens at the front motor mounts. The back motor-mount bolt holes line up with the stock extrusion's existing holes. To use the stock 345mm extrusion without cutting it, fit a 6mm OD (or smaller) M3 x 20mm spacer in the spot nearest each end of this extrusion (one per back corner) instead of an 8mm one.</t>
+          <t>Shortened from 345mm: all tensioning now happens at the front motor mounts. The back motor-mount bolt holes line up with the stock extrusion's existing holes. To use the stock 345mm extrusion without cutting it, fit a 6mm OD (or smaller) M3 x 20mm spacer in the spot nearest each end of this extrusion (one per back corner) instead of an 8mm one. If you cut a 345mm extrusion down to 342mm, take 1.5mm off each end: the stock holes are 5mm and 23mm from each end, so an even trim keeps both ends lined up with the back motor-mount holes.</t>
         </is>
       </c>
     </row>
